--- a/output/projects/Sorsele/excel/ArbetsExcel_Sorsele_byggd.xlsx
+++ b/output/projects/Sorsele/excel/ArbetsExcel_Sorsele_byggd.xlsx
@@ -10,10 +10,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa_från_edp" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Körningsinfo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taxa_Förslag" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Avfall" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Slam" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard ÅVS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Avviker_Standard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelspårning" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Avfall" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard Slam" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EDP_Standard_Standard ÅVS" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -600,7 +601,28 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RegelsparningTable" displayName="RegelsparningTable" ref="A6:J7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EdpAvvikerStandardTable" displayName="EdpAvvikerStandardTable" ref="A6:L7" headerRowCount="1">
+  <autoFilter ref="A6:L7"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Kommun"/>
+    <tableColumn id="2" name="EDP taxekod"/>
+    <tableColumn id="3" name="EDP benämning"/>
+    <tableColumn id="4" name="EDP faktor"/>
+    <tableColumn id="5" name="EDP taxedel"/>
+    <tableColumn id="6" name="Standard taxekod"/>
+    <tableColumn id="7" name="Standard benämning"/>
+    <tableColumn id="8" name="Standard faktor"/>
+    <tableColumn id="9" name="Standard taxedel"/>
+    <tableColumn id="10" name="Avvikelse"/>
+    <tableColumn id="11" name="Rekommendation"/>
+    <tableColumn id="12" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="RegelsparningTable" displayName="RegelsparningTable" ref="A6:J7" headerRowCount="1">
   <autoFilter ref="A6:J7"/>
   <tableColumns count="10">
     <tableColumn id="1" name="Kommun"/>
@@ -21330,7 +21352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -21398,36 +21420,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Standardtaxor</t>
+          <t>EDP-regel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inkluderade som referensflikar om standardtaxefilen finns</t>
+          <t>Taxor i Taxa_från_edp är fasta och ändras inte automatiskt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Taxa_Förslag</t>
+          <t>Standardtaxor</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ingår i alla outputfiler för föreslagna saknade taxekoder</t>
+          <t>Inkluderade som referensflikar om standardtaxefilen finns</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Taxa_Förslag</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ingår för föreslagna saknade taxekoder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EDP_Avviker_Standard</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ingår för avvikelser mot standardtaxor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Regelspårning</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ingår i alla outputfiler för spårbarhet av beslut/regler</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ingår för spårbarhet av beslut/regler</t>
         </is>
       </c>
     </row>
@@ -21601,6 +21647,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>EDP Export avviker från standardtaxa</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Syfte</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Visar avvikelser mot standardtaxor. Befintlig Taxa_från_edp är fast och ändras aldrig automatiskt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Källa</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>EDP-export: data\edp_exports\Sorsele.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Kommun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>EDP taxekod</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>EDP benämning</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>EDP faktor</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>EDP taxedel</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Standard taxekod</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Standard benämning</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Standard faktor</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Standard taxedel</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Avvikelse</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Rekommendation</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Granska manuellt. Ändra inte befintlig EDP automatiskt.</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Ej granskad</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -21610,7 +21818,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
@@ -21732,7 +21940,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Taxakod får endast sättas från säker EDP-match eller markerat förslag.</t>
+          <t>Befintlig Taxa_från_edp är fast. Standardtaxor får endast ge förslag/avvikelse.</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -21759,7 +21967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35199,7 +35407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38872,7 +39080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/projects/Sorsele/excel/ArbetsExcel_Sorsele_byggd.xlsx
+++ b/output/projects/Sorsele/excel/ArbetsExcel_Sorsele_byggd.xlsx
@@ -1079,8 +1079,6 @@
           <t>Avlopp bostadshus</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>2762.0</t>
@@ -1096,7 +1094,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1107,7 +1104,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1150,8 +1146,6 @@
           <t>Avlopp fritidshus</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>1939.0</t>
@@ -1167,7 +1161,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>-</t>
@@ -1178,7 +1171,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1221,8 +1213,6 @@
           <t>Avlopp fritidshus</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>1112.0</t>
@@ -1238,7 +1228,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>-</t>
@@ -1296,8 +1285,6 @@
           <t>Extraavg akut slamtömning</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -1313,7 +1300,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>-</t>
@@ -1371,8 +1357,6 @@
           <t>Avgift för akutsäck</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -1388,7 +1372,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>-</t>
@@ -1426,7 +1409,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1442,8 +1424,6 @@
           <t>Amorteringsplanavisering</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>20.0</t>
@@ -1459,7 +1439,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1470,7 +1449,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1493,7 +1471,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1509,16 +1486,11 @@
           <t>Amorteringsplan</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>-</t>
@@ -1556,7 +1528,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1572,8 +1543,6 @@
           <t>Amorteringsplanränta</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1589,7 +1558,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>-</t>
@@ -1600,7 +1568,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1623,7 +1590,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1639,8 +1605,6 @@
           <t>Amorteringsplansuppläggning</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>150.0</t>
@@ -1656,7 +1620,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>-</t>
@@ -1667,7 +1630,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1710,8 +1672,6 @@
           <t>Tömning av slamanläggning</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>1420.0</t>
@@ -1727,7 +1687,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>-</t>
@@ -1785,8 +1744,6 @@
           <t>Tömning av slamanlägg. 3,1-6</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>1920.0</t>
@@ -1802,7 +1759,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>-</t>
@@ -1860,8 +1816,6 @@
           <t>Tömning slam från Reningsverksbassäng</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1877,7 +1831,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>-</t>
@@ -1935,8 +1888,6 @@
           <t>Tömning av slamanlägg över 6 m³</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>2448.0</t>
@@ -1952,7 +1903,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>-</t>
@@ -2010,8 +1960,6 @@
           <t>Avlopp obebygg inom detaljp</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>2200.0</t>
@@ -2027,7 +1975,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>-</t>
@@ -2038,7 +1985,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2081,16 +2027,11 @@
           <t>Avslut av tjänst</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>-</t>
@@ -2148,8 +2089,6 @@
           <t>Reningsverksbassäng, slam. Ord. tur Kommunal</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2165,7 +2104,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>-</t>
@@ -2223,8 +2161,6 @@
           <t>BDT 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>800.0</t>
@@ -2240,7 +2176,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>-</t>
@@ -2298,8 +2233,6 @@
           <t>BDT 0-3 m³, slam. Ord. tur</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>1420.0</t>
@@ -2315,7 +2248,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>-</t>
@@ -2373,8 +2305,6 @@
           <t>BDT 3,1-6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2390,7 +2320,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>-</t>
@@ -2448,8 +2377,6 @@
           <t>BDT 3,1-6 m³, slam. Ord. tur</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2465,7 +2392,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>-</t>
@@ -2523,8 +2449,6 @@
           <t>BDT över 6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2540,7 +2464,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>-</t>
@@ -2598,8 +2521,6 @@
           <t>BDT över 6 m³, slam. Ord. tur</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2615,7 +2536,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>-</t>
@@ -2673,8 +2593,6 @@
           <t>Behandlingsavgift Aska</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>650.0</t>
@@ -2690,7 +2608,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>-</t>
@@ -2748,8 +2665,6 @@
           <t>Behandlingsavgift Restavfall</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>2500.0</t>
@@ -2765,7 +2680,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>-</t>
@@ -2823,8 +2737,6 @@
           <t>Behandlingsavgift Slam</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2840,7 +2752,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>-</t>
@@ -2898,8 +2809,6 @@
           <t>Behandlingsavgift Slam</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2915,7 +2824,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>-</t>
@@ -2973,8 +2881,6 @@
           <t>Betalsäck, pris per säck</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -2990,7 +2896,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>-</t>
@@ -3048,8 +2953,6 @@
           <t>Bini 1000 lastväxlare</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>248.0</t>
@@ -3065,7 +2968,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>-</t>
@@ -3123,8 +3025,6 @@
           <t>Bini 610/500</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>240.0</t>
@@ -3140,7 +3040,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>-</t>
@@ -3198,8 +3097,6 @@
           <t>Brunn 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3215,7 +3112,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3273,8 +3169,6 @@
           <t>Brunn 0-3 m³, slam. Ord. tur</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3290,7 +3184,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>-</t>
@@ -3348,8 +3241,6 @@
           <t>Brunn 3,1-6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3365,7 +3256,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>-</t>
@@ -3423,8 +3313,6 @@
           <t>Brunn över 6 m³, slam. Ord. tur</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3440,7 +3328,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>-</t>
@@ -3498,8 +3385,6 @@
           <t>Brunn över 6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3515,7 +3400,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>-</t>
@@ -3573,8 +3457,6 @@
           <t>Brunn över 6 m³, slam. Ord. tur</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3590,7 +3472,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>-</t>
@@ -3648,8 +3529,6 @@
           <t>Brännbart avfall</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>2500.0</t>
@@ -3665,7 +3544,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>-</t>
@@ -3723,8 +3601,6 @@
           <t>Byte av sopkärl</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>192.0</t>
@@ -3740,7 +3616,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>-</t>
@@ -3798,8 +3673,6 @@
           <t>Container 10m3 Aska</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3815,7 +3688,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>-</t>
@@ -3873,8 +3745,6 @@
           <t>Container 12m3 6-fack</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3890,7 +3760,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>-</t>
@@ -3948,8 +3817,6 @@
           <t>Container 12 m3, Slam</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3965,7 +3832,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4023,8 +3889,6 @@
           <t>Sophämtning delat 190 l kärl</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>706.0</t>
@@ -4040,7 +3904,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>-</t>
@@ -4078,7 +3941,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>1</t>
@@ -4094,8 +3956,6 @@
           <t>Dröjsmålsränta</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4111,7 +3971,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>-</t>
@@ -4122,7 +3981,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4165,8 +4023,6 @@
           <t>Evenemangskärl 140 L, matavfall</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>1000.0</t>
@@ -4182,7 +4038,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>-</t>
@@ -4240,8 +4095,6 @@
           <t>Evenemangskärl 190 L, restavfall</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -4257,7 +4110,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>-</t>
@@ -4315,8 +4167,6 @@
           <t>Evenemangskärl 660 L, restavfall</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>2000.0</t>
@@ -4332,7 +4182,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4390,8 +4239,6 @@
           <t>Tjänsttaxa för evenemangskärl</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4407,7 +4254,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>-</t>
@@ -4465,8 +4311,6 @@
           <t>Förseningsavgift efteranmälan</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -4482,7 +4326,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>-</t>
@@ -4540,8 +4383,6 @@
           <t>Budning av farligt avfall, pris per tillfälle</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>1600.0</t>
@@ -4557,7 +4398,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>-</t>
@@ -4615,8 +4455,6 @@
           <t>Felsorteringsavgift, pris per tillfälle och kärl</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -4632,7 +4470,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>-</t>
@@ -4690,8 +4527,6 @@
           <t>Filmning/besiktning</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>113.6</t>
@@ -4707,7 +4542,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>-</t>
@@ -4765,8 +4599,6 @@
           <t>Fjärrvärme</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>424.0</t>
@@ -4782,7 +4614,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>-</t>
@@ -4793,7 +4624,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4836,8 +4666,6 @@
           <t>Framkörningsavgift</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>652.0</t>
@@ -4853,7 +4681,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>-</t>
@@ -4891,7 +4718,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>1</t>
@@ -4907,8 +4733,6 @@
           <t>Fri faktura, standard</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4924,7 +4748,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>-</t>
@@ -4935,7 +4758,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4958,7 +4780,6 @@
           <t>AD</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>1</t>
@@ -4969,9 +4790,6 @@
           <t>KVAN</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4987,7 +4805,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>-</t>
@@ -5025,7 +4842,6 @@
           <t>AD</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>1</t>
@@ -5036,9 +4852,6 @@
           <t>KVAN</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>123.0</t>
@@ -5054,7 +4867,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>-</t>
@@ -5112,8 +4924,6 @@
           <t>Byte av frusen mätare</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>720.0</t>
@@ -5129,7 +4939,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5187,8 +4996,6 @@
           <t>Hämtningavgift gemensam uppsamlingsplats, eget kärl</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>280.0</t>
@@ -5204,7 +5011,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>-</t>
@@ -5262,8 +5068,6 @@
           <t>Viktavgift rest- matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -5279,7 +5083,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>-</t>
@@ -5337,8 +5140,6 @@
           <t>LIP, mat- och restavfall</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -5354,7 +5155,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>-</t>
@@ -5412,8 +5212,6 @@
           <t>Telefonnyckel nr 3 Gemlipfri</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -5429,7 +5227,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>-</t>
@@ -5440,7 +5237,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5483,8 +5279,6 @@
           <t>Telefonnyckel nr 4 Gemlipfri</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -5500,7 +5294,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>-</t>
@@ -5511,7 +5304,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5554,8 +5346,6 @@
           <t>Tagg Gemlipfri</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -5571,7 +5361,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>-</t>
@@ -5582,7 +5371,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5625,8 +5413,6 @@
           <t>Grund och mätaravgift</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>2884.0</t>
@@ -5642,7 +5428,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>-</t>
@@ -5653,7 +5438,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5696,8 +5480,6 @@
           <t>Grovavfall/organiskt avfall, storkompost</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>260.0</t>
@@ -5713,7 +5495,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>-</t>
@@ -5771,8 +5552,6 @@
           <t>Budning av grovavfall, pris per tillfälle</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>1600.0</t>
@@ -5788,7 +5567,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>-</t>
@@ -5846,8 +5624,6 @@
           <t>Grundavgift per lägenhet</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>562.5</t>
@@ -5863,7 +5639,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>-</t>
@@ -5921,8 +5696,6 @@
           <t>Grundavg. renhåll. fritid</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>1040.0</t>
@@ -5938,7 +5711,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>-</t>
@@ -5949,7 +5721,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5992,8 +5763,6 @@
           <t>Grundavgift nivå 1</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>4500.0</t>
@@ -6009,7 +5778,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>-</t>
@@ -6020,7 +5788,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6063,8 +5830,6 @@
           <t>Grundavgift nivå 2</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>6000.0</t>
@@ -6080,7 +5845,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>-</t>
@@ -6091,7 +5855,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6134,8 +5897,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>960.0</t>
@@ -6151,7 +5912,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>-</t>
@@ -6162,7 +5922,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6205,8 +5964,6 @@
           <t>Grundavgift per lägenhet</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>680.0</t>
@@ -6222,7 +5979,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>-</t>
@@ -6280,8 +6036,6 @@
           <t>Grundavgift renhållning perm.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>1280.0</t>
@@ -6297,7 +6051,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>-</t>
@@ -6308,7 +6061,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6351,8 +6103,6 @@
           <t>Grundavgift permanentboende</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>936.0</t>
@@ -6368,7 +6118,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>-</t>
@@ -6379,7 +6128,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6422,8 +6170,6 @@
           <t>14-dagars hämtning 120 l kärl</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>1340.0</t>
@@ -6439,7 +6185,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>-</t>
@@ -6497,8 +6242,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>936.0</t>
@@ -6514,7 +6257,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>-</t>
@@ -6525,7 +6267,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6568,8 +6309,6 @@
           <t>14-dagars hämtning 190 l kärl</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>2336.0</t>
@@ -6585,7 +6324,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>-</t>
@@ -6643,8 +6381,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>936.0</t>
@@ -6660,7 +6396,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>-</t>
@@ -6671,7 +6406,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6714,8 +6448,6 @@
           <t>190 L KÄRL tillf tjänst</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>396.15</t>
@@ -6731,7 +6463,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>-</t>
@@ -6789,8 +6520,6 @@
           <t>14-dagars hämtning 370 l kärl</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>3632.0</t>
@@ -6806,7 +6535,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>-</t>
@@ -6864,8 +6592,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>936.0</t>
@@ -6881,7 +6607,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>-</t>
@@ -6892,7 +6617,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6935,8 +6659,6 @@
           <t>14-dagars hämtning 660 l kärl</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>6240.0</t>
@@ -6952,7 +6674,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>-</t>
@@ -7010,8 +6731,6 @@
           <t>Hyra container 3 m³</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>21900.0</t>
@@ -7027,7 +6746,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>-</t>
@@ -7085,8 +6803,6 @@
           <t>Hyra container 5 m³</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>29200.0</t>
@@ -7102,7 +6818,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>-</t>
@@ -7160,8 +6875,6 @@
           <t>Hyra container 8 m³</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>36500.0</t>
@@ -7177,7 +6890,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>-</t>
@@ -7235,8 +6947,6 @@
           <t>14-dagars hämtning 120 l kärl</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>832.0</t>
@@ -7252,7 +6962,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>-</t>
@@ -7310,8 +7019,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>580.0</t>
@@ -7327,7 +7034,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>-</t>
@@ -7338,7 +7044,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7381,8 +7086,6 @@
           <t>14-dagars hämtning 190 l kärl</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>1216.0</t>
@@ -7398,7 +7101,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>-</t>
@@ -7456,8 +7158,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>580.0</t>
@@ -7473,7 +7173,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>-</t>
@@ -7484,7 +7183,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7527,8 +7225,6 @@
           <t>190 L KÄRL tillf tjänst</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>207.13</t>
@@ -7544,7 +7240,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>-</t>
@@ -7602,8 +7297,6 @@
           <t>14-dagars hämtning 370 l kärl</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>1784.0</t>
@@ -7619,7 +7312,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>-</t>
@@ -7677,8 +7369,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>580.0</t>
@@ -7694,7 +7384,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>-</t>
@@ -7705,7 +7394,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7748,8 +7436,6 @@
           <t>Sophämtning 120 l kärl</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
           <t>1340.0</t>
@@ -7765,7 +7451,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>-</t>
@@ -7823,8 +7508,6 @@
           <t>Sophämtning 190 l kärl</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>2336.0</t>
@@ -7840,7 +7523,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>-</t>
@@ -7898,8 +7580,6 @@
           <t>Sophämtning 370 l kärl</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
           <t>3632.0</t>
@@ -7915,7 +7595,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>-</t>
@@ -7973,8 +7652,6 @@
           <t>Sophämtning 660 l kärl</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
           <t>6240.0</t>
@@ -7990,7 +7667,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>-</t>
@@ -8048,8 +7724,6 @@
           <t>Sophämtning 120 lit kärl</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
           <t>832.0</t>
@@ -8065,7 +7739,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>-</t>
@@ -8123,8 +7796,6 @@
           <t>Sophämtning 370 l kärl</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
           <t>1784.0</t>
@@ -8140,7 +7811,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>-</t>
@@ -8198,8 +7868,6 @@
           <t>Hämtning av farligt avfall, pris per tillfälle</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
           <t>2000.0</t>
@@ -8215,7 +7883,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>-</t>
@@ -8273,8 +7940,6 @@
           <t>Inert avfall. Tex klinker, porslin, toalettstolar</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
           <t>1800.0</t>
@@ -8290,7 +7955,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>-</t>
@@ -8328,7 +7992,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>1</t>
@@ -8344,8 +8007,6 @@
           <t>Inkassoavgift</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -8361,7 +8022,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>-</t>
@@ -8372,7 +8032,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8395,7 +8054,6 @@
           <t>RENH</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>1</t>
@@ -8411,8 +8069,6 @@
           <t>Kreditering av grundavgifter april/maj 2023</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8428,7 +8084,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>-</t>
@@ -8486,8 +8141,6 @@
           <t>Kärl 140 L matavfall FLB/VHT</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
           <t>500.0</t>
@@ -8503,7 +8156,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>-</t>
@@ -8561,8 +8213,6 @@
           <t>Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -8578,7 +8228,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>-</t>
@@ -8636,8 +8285,6 @@
           <t>Vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -8653,7 +8300,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>-</t>
@@ -8711,8 +8357,6 @@
           <t>Kärlavgift 140 L kärl, matavfall. Var 14:e dag</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8728,7 +8372,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>-</t>
@@ -8786,8 +8429,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8803,7 +8444,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>-</t>
@@ -8861,8 +8501,6 @@
           <t>Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8878,7 +8516,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>-</t>
@@ -8936,8 +8573,6 @@
           <t>Extra kärl 140 L, matavfall</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
           <t>240.0</t>
@@ -8953,7 +8588,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>-</t>
@@ -9011,8 +8645,6 @@
           <t>Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -9028,7 +8660,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr">
         <is>
           <t>-</t>
@@ -9086,8 +8717,6 @@
           <t>Vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -9103,7 +8732,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr">
         <is>
           <t>-</t>
@@ -9161,8 +8789,6 @@
           <t>Extra kärl 140 L, restavfall</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
           <t>240.0</t>
@@ -9178,7 +8804,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr">
         <is>
           <t>-</t>
@@ -9236,8 +8861,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -9253,7 +8876,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr">
         <is>
           <t>-</t>
@@ -9311,8 +8933,6 @@
           <t>Vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
           <t>8.0</t>
@@ -9328,7 +8948,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr">
         <is>
           <t>-</t>
@@ -9386,8 +9005,6 @@
           <t>Kärl 240L , restavfall/kompost</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -9403,7 +9020,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>-</t>
@@ -9461,8 +9077,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -9478,7 +9092,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
           <t>-</t>
@@ -9536,8 +9149,6 @@
           <t>Tvåfackskärl , rest/matavfall.</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -9553,7 +9164,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
           <t>-</t>
@@ -9611,8 +9221,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -9628,7 +9236,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
           <t>-</t>
@@ -9686,8 +9293,6 @@
           <t>Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -9703,7 +9308,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
           <t>-</t>
@@ -9761,8 +9365,6 @@
           <t>Kärl 240L , rest/mat FLB/VHT</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -9778,7 +9380,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
           <t>-</t>
@@ -9836,8 +9437,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -9853,7 +9452,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
           <t>-</t>
@@ -9911,8 +9509,6 @@
           <t>Viktavgift matavfall kr/kg</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -9928,7 +9524,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr">
         <is>
           <t>-</t>
@@ -9986,8 +9581,6 @@
           <t>Kärl 370 L kärl, rest. FLB/VHT</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
           <t>800.0</t>
@@ -10003,7 +9596,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
           <t>-</t>
@@ -10061,8 +9653,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -10078,7 +9668,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
           <t>-</t>
@@ -10136,8 +9725,6 @@
           <t>Avgift över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
           <t>7.5</t>
@@ -10153,7 +9740,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
           <t>-</t>
@@ -10211,8 +9797,6 @@
           <t>Kärl 660 L, rest. FLB/VHT</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
           <t>1040.0</t>
@@ -10228,7 +9812,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr">
         <is>
           <t>-</t>
@@ -10286,8 +9869,6 @@
           <t>Viktavgift restavfall kr/kg</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -10303,7 +9884,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr">
         <is>
           <t>-</t>
@@ -10361,8 +9941,6 @@
           <t>Avgift över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
           <t>7.5</t>
@@ -10378,7 +9956,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr">
         <is>
           <t>-</t>
@@ -10436,16 +10013,11 @@
           <t>Kärl 660 L, rest. FLB/VHT</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
           <t>-</t>
@@ -10503,8 +10075,6 @@
           <t>Byte/återtag av behållare 140–240 L, 1 ggr/år</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>200.0</t>
@@ -10520,7 +10090,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr">
         <is>
           <t>-</t>
@@ -10578,8 +10147,6 @@
           <t>Byte/återtag av behållare 370–660 L, 1 ggr/år</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>320.0</t>
@@ -10595,7 +10162,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr">
         <is>
           <t>-</t>
@@ -10653,8 +10219,6 @@
           <t>Ytterligare byte av kärl under kalenderåret</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -10670,7 +10234,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
           <t>-</t>
@@ -10728,8 +10291,6 @@
           <t>Extra slang &gt; 5 m</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
           <t>480.0</t>
@@ -10745,7 +10306,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>-</t>
@@ -10803,8 +10363,6 @@
           <t>Avgift för latrinbehållare</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>360.0</t>
@@ -10820,7 +10378,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>-</t>
@@ -10878,8 +10435,6 @@
           <t>MAN Lastbil</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
           <t>258.4</t>
@@ -10895,7 +10450,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>-</t>
@@ -10953,8 +10507,6 @@
           <t>Tömning Markbehållare 1.4 m³, glas färgat.</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10970,7 +10522,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>-</t>
@@ -11028,8 +10579,6 @@
           <t>Tömning Markbehållare 1.4 m³, glas färgat.</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11045,7 +10594,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>-</t>
@@ -11103,8 +10651,6 @@
           <t>Tömning Markbehållare 1.4 m³, glas ofärgat.</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11120,7 +10666,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>-</t>
@@ -11178,8 +10723,6 @@
           <t>TTömning Markbehållare 1.4 m³, glas ofärgat.</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11195,7 +10738,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>-</t>
@@ -11253,8 +10795,6 @@
           <t>Tömning Markbehållare 1.4 m³, matavfall.</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11270,7 +10810,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>-</t>
@@ -11328,8 +10867,6 @@
           <t>Tömning Markbehållare 1.4 m³, matavfall</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11345,7 +10882,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>-</t>
@@ -11403,8 +10939,6 @@
           <t>Tömning Markbehållare 1.4 m³, metallförpackningar.</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11420,7 +10954,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>-</t>
@@ -11478,8 +11011,6 @@
           <t>Tömning Markbehållare 1.4 m³, metallförpackningar.</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11495,7 +11026,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
           <t>-</t>
@@ -11553,8 +11083,6 @@
           <t>Tömning Markbehållare 1.4 m³, tidningar.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11570,7 +11098,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>-</t>
@@ -11628,8 +11155,6 @@
           <t>Tömning Markbehållare 1.4 m³, tidningar.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11645,7 +11170,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
           <t>-</t>
@@ -11703,8 +11227,6 @@
           <t>Tömning Markbehållare 1.4 m³, matavfall</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11720,7 +11242,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>-</t>
@@ -11778,8 +11299,6 @@
           <t>Tömning Markbehållare 2,6 m³, pappersförpackningar.</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11795,7 +11314,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>-</t>
@@ -11853,8 +11371,6 @@
           <t>Tömning Markbehållare 2,6 m³, pappersförpackningar.</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11870,7 +11386,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>-</t>
@@ -11928,8 +11443,6 @@
           <t>Tömning Markbehållare 2,6 m³, plastförpackning.</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -11945,7 +11458,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>-</t>
@@ -12003,8 +11515,6 @@
           <t>Tömning Markbehållare 2,6 m³, plastförpackning.</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12020,7 +11530,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>-</t>
@@ -12078,8 +11587,6 @@
           <t>Tömning Markbehållare 2,6 m³, restavfall.</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12095,7 +11602,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>-</t>
@@ -12153,8 +11659,6 @@
           <t>Tömning Markbehållare 2,6 m³, restavfall.</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12170,7 +11674,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
           <t>-</t>
@@ -12228,8 +11731,6 @@
           <t>MB Sprinter</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>160.0</t>
@@ -12245,7 +11746,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
           <t>-</t>
@@ -12303,8 +11803,6 @@
           <t>Metallskrot- rent</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12320,7 +11818,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
           <t>-</t>
@@ -12378,8 +11875,6 @@
           <t>Miljöfarligt avfall nivå 1</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
           <t>4500.0</t>
@@ -12395,7 +11890,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>-</t>
@@ -12406,7 +11900,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -12449,8 +11942,6 @@
           <t>Miljöfarligt avfall nivå 2</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
           <t>9000.0</t>
@@ -12466,7 +11957,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr">
         <is>
           <t>-</t>
@@ -12477,7 +11967,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -12520,8 +12009,6 @@
           <t>Minireningsverk 0-3 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12537,7 +12024,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
           <t>-</t>
@@ -12595,8 +12081,6 @@
           <t>Minireningsverk 0-3 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12612,7 +12096,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
           <t>-</t>
@@ -12670,8 +12153,6 @@
           <t>Minireningsverk 3,1-6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12687,7 +12168,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
           <t>-</t>
@@ -12745,8 +12225,6 @@
           <t>Minireningsverk 3,1-6 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12762,7 +12240,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr">
         <is>
           <t>-</t>
@@ -12820,8 +12297,6 @@
           <t>Minireningsverk över 6 m³, slam. Budning</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12837,7 +12312,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr">
         <is>
           <t>-</t>
@@ -12895,8 +12369,6 @@
           <t>Minireningsverk över 6 m³, slam. Ordinarie tur</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -12912,7 +12384,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr">
         <is>
           <t>-</t>
@@ -12970,16 +12441,11 @@
           <t>Tvåfackskärl , rest/matavfall.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr">
         <is>
           <t>-</t>
@@ -13037,16 +12503,11 @@
           <t>Dummytaxa, ny tjänst via ändringsorder</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr">
         <is>
           <t>-</t>
@@ -13104,8 +12565,6 @@
           <t>Obebott, avlopp</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
           <t>2200.0</t>
@@ -13121,7 +12580,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr">
         <is>
           <t>-</t>
@@ -13132,7 +12590,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -13175,8 +12632,6 @@
           <t>Omklassning av felsorterad container</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
           <t>1710.0</t>
@@ -13192,7 +12647,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr">
         <is>
           <t>-</t>
@@ -13250,8 +12704,6 @@
           <t>Orderrad för trasigt kärl, byta/laga</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13267,7 +12719,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
           <t>-</t>
@@ -13325,8 +12776,6 @@
           <t>Obebott, vatten</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
           <t>2288.0</t>
@@ -13342,7 +12791,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr">
         <is>
           <t>-</t>
@@ -13353,7 +12801,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -13396,8 +12843,6 @@
           <t>Obebott, vatten och avlopp</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
           <t>4293.0</t>
@@ -13413,7 +12858,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
           <t>-</t>
@@ -13424,7 +12868,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -13467,8 +12910,6 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr">
         <is>
           <t>233.6</t>
@@ -13484,7 +12925,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
           <t>-</t>
@@ -13542,8 +12982,6 @@
           <t>Personbil</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
           <t>152.0</t>
@@ -13559,7 +12997,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr">
         <is>
           <t>-</t>
@@ -13597,7 +13034,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>1</t>
@@ -13613,8 +13049,6 @@
           <t>Påminnelsavgift</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
-      <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
           <t>50.0</t>
@@ -13630,7 +13064,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
           <t>-</t>
@@ -13641,7 +13074,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13684,8 +13116,6 @@
           <t>Tömning av resurskärl</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
           <t>400.0</t>
@@ -13701,7 +13131,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
           <t>-</t>
@@ -13739,7 +13168,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>1</t>
@@ -13755,8 +13183,6 @@
           <t>Restskuld</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13772,7 +13198,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr">
         <is>
           <t>-</t>
@@ -13783,7 +13208,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -13806,7 +13230,6 @@
           <t>RENH</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>1</t>
@@ -13822,8 +13245,6 @@
           <t>Renh, tillägg-avdrag</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
-      <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -13839,7 +13260,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr">
         <is>
           <t>-</t>
@@ -13850,7 +13270,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -13893,8 +13312,6 @@
           <t>Sophämtning samlingskärl</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
-      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
           <t>472.0</t>
@@ -13910,7 +13327,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr">
         <is>
           <t>-</t>
@@ -13921,7 +13337,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -13964,8 +13379,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
           <t>536.0</t>
@@ -13981,7 +13394,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
           <t>-</t>
@@ -13992,7 +13404,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -14035,8 +13446,6 @@
           <t>Sophämtning samlingskärl</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
           <t>920.0</t>
@@ -14052,7 +13461,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>-</t>
@@ -14063,7 +13471,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -14106,8 +13513,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
           <t>864.0</t>
@@ -14123,7 +13528,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
           <t>-</t>
@@ -14134,7 +13538,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -14177,8 +13580,6 @@
           <t>Sophämtning samlingskärl</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
           <t>364.0</t>
@@ -14194,7 +13595,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr">
         <is>
           <t>-</t>
@@ -14205,7 +13605,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14248,8 +13647,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
           <t>332.0</t>
@@ -14265,7 +13662,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
           <t>-</t>
@@ -14276,7 +13672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -14319,8 +13714,6 @@
           <t>Sophämtning samlingskärl</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
           <t>472.0</t>
@@ -14336,7 +13729,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr">
         <is>
           <t>-</t>
@@ -14347,7 +13739,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -14390,8 +13781,6 @@
           <t>Grundavgift</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
           <t>536.0</t>
@@ -14407,7 +13796,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
           <t>-</t>
@@ -14418,7 +13806,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -14461,8 +13848,6 @@
           <t>Tillägg för akut tömning</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -14478,7 +13863,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr">
         <is>
           <t>-</t>
@@ -14536,8 +13920,6 @@
           <t>Tömning av slambrunn</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
           <t>1392.0</t>
@@ -14553,7 +13935,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr">
         <is>
           <t>-</t>
@@ -14611,8 +13992,6 @@
           <t>Tömning av slambrunn</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
           <t>1880.0</t>
@@ -14628,7 +14007,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr">
         <is>
           <t>-</t>
@@ -14686,8 +14064,6 @@
           <t>Slam &gt;3 kbm</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -14703,7 +14079,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr">
         <is>
           <t>-</t>
@@ -14761,8 +14136,6 @@
           <t>Extra slang &gt; 5 m</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -14778,7 +14151,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
           <t>-</t>
@@ -14836,8 +14208,6 @@
           <t>Tömn av slambrunn över 6 kbm</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
           <t>2400.0</t>
@@ -14853,7 +14223,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr">
         <is>
           <t>-</t>
@@ -14911,8 +14280,6 @@
           <t>Slam &gt;6 kbm</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -14928,7 +14295,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr">
         <is>
           <t>-</t>
@@ -14986,8 +14352,6 @@
           <t>Extra slang &gt; 5 m</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15003,7 +14367,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
           <t>-</t>
@@ -15061,8 +14424,6 @@
           <t>Slam &lt;3 kbm</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15078,7 +14439,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
           <t>-</t>
@@ -15136,8 +14496,6 @@
           <t>Extra slang &gt; 5 m</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15153,7 +14511,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
           <t>-</t>
@@ -15211,8 +14568,6 @@
           <t>Tömning av slambrunn</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15228,7 +14583,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr">
         <is>
           <t>-</t>
@@ -15286,8 +14640,6 @@
           <t>Slanglängd</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15303,7 +14655,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr">
         <is>
           <t>-</t>
@@ -15361,8 +14712,6 @@
           <t>Rolba slamtunna</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
           <t>280.8</t>
@@ -15378,7 +14727,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr">
         <is>
           <t>-</t>
@@ -15436,8 +14784,6 @@
           <t>Tillägg för avropad/budad tömning</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
           <t>1200.0</t>
@@ -15453,7 +14799,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr">
         <is>
           <t>-</t>
@@ -15511,8 +14856,6 @@
           <t>Avgift avsteg från gällande abonnemang</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -15528,7 +14871,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr">
         <is>
           <t>-</t>
@@ -15586,8 +14928,6 @@
           <t>Framkörningsavgift slam</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
           <t>640.0</t>
@@ -15603,7 +14943,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr">
         <is>
           <t>-</t>
@@ -15661,8 +15000,6 @@
           <t>Avgift för ej uppfyllt meddelaransvar</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
           <t>250.0</t>
@@ -15678,7 +15015,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr">
         <is>
           <t>-</t>
@@ -15736,8 +15072,6 @@
           <t>Slam, tillägg för slangdragning</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
           <t>492.0</t>
@@ -15753,7 +15087,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
         <is>
           <t>-</t>
@@ -15811,8 +15144,6 @@
           <t>Slam, tillägg för slangdragning</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15828,7 +15159,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr">
         <is>
           <t>-</t>
@@ -15886,8 +15216,6 @@
           <t>Sluten tank 0-3 m³, slam. Bud</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15903,7 +15231,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr">
         <is>
           <t>-</t>
@@ -15961,8 +15288,6 @@
           <t>Sluten tank 0-3 m³, slam. Ord</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -15978,7 +15303,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr">
         <is>
           <t>-</t>
@@ -16036,8 +15360,6 @@
           <t>Sluten tank 3,1-6 m³, slam. Bud</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16053,7 +15375,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
           <t>-</t>
@@ -16111,8 +15432,6 @@
           <t>Sluten tank 3,1-6 m³, slam. Ord</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16128,7 +15447,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr">
         <is>
           <t>-</t>
@@ -16186,8 +15504,6 @@
           <t>Tömning överstigande 1 timme</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
           <t>1530.0</t>
@@ -16203,7 +15519,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr">
         <is>
           <t>-</t>
@@ -16261,8 +15576,6 @@
           <t>Tömning av toalettvagn eller liknande</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
           <t>2000.0</t>
@@ -16278,7 +15591,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr">
         <is>
           <t>-</t>
@@ -16336,8 +15648,6 @@
           <t>Lyft av tungt brunnslock över 15 kg</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
           <t>950.0</t>
@@ -16353,7 +15663,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
           <t>-</t>
@@ -16411,8 +15720,6 @@
           <t>Sluten tank över 6 m³, slam. Bud</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16428,7 +15735,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr">
         <is>
           <t>-</t>
@@ -16486,8 +15792,6 @@
           <t>Sluten tank över 6 m³, slam. Ord</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -16503,7 +15807,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr">
         <is>
           <t>-</t>
@@ -16561,8 +15864,6 @@
           <t>Material till sortering</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
           <t>4000.0</t>
@@ -16578,7 +15879,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr">
         <is>
           <t>-</t>
@@ -16636,8 +15936,6 @@
           <t>Spolvagn</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
-      <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
           <t>269.6</t>
@@ -16653,7 +15951,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
           <t>-</t>
@@ -16711,16 +16008,11 @@
           <t>Kärl 370 L kärl test papper plast</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
           <t>X</t>
@@ -16778,16 +16070,11 @@
           <t>Kärl 370 L kärl test viktavgift papper plast</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
           <t>X</t>
@@ -16845,16 +16132,11 @@
           <t>240 L kärl/4:e vecka metall textil TEST</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
           <t>-</t>
@@ -16912,16 +16194,11 @@
           <t>240 L kärl viktavgift metall textil TEST</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
-      <c r="J217" t="inlineStr"/>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
           <t>-</t>
@@ -16979,16 +16256,11 @@
           <t>240 l kärl/4 vecka test glas färgat ofärgata</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
-      <c r="J218" t="inlineStr"/>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr">
         <is>
           <t>X</t>
@@ -17046,16 +16318,11 @@
           <t>240 l viktavgift färgat ofärgat test</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
           <t>X</t>
@@ -17093,7 +16360,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
       <c r="F220" t="inlineStr">
         <is>
           <t>1</t>
@@ -17109,8 +16375,6 @@
           <t>Kreditavdrag</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17126,7 +16390,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
           <t>-</t>
@@ -17137,7 +16400,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="Q220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -17180,8 +16442,6 @@
           <t>Träavfall- behandlat</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
           <t>1600.0</t>
@@ -17197,7 +16457,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr">
         <is>
           <t>-</t>
@@ -17255,8 +16514,6 @@
           <t>Budning av trädgårdsavfall, pris per tillfälle</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
           <t>1600.0</t>
@@ -17272,7 +16529,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
         <is>
           <t>-</t>
@@ -17330,8 +16586,6 @@
           <t>Träavfall- rent</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
-      <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
           <t>950.0</t>
@@ -17347,7 +16601,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr">
         <is>
           <t>-</t>
@@ -17405,8 +16658,6 @@
           <t>Lyft av tungt brunnslock över 15 kg</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
           <t>776.0</t>
@@ -17422,7 +16673,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr">
         <is>
           <t>-</t>
@@ -17480,8 +16730,6 @@
           <t>Underjordsbehållare 1,5 m³, glas färgat</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17497,7 +16745,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
           <t>-</t>
@@ -17555,8 +16802,6 @@
           <t>Tömning underjordsbehållare 1,5 m³, glasförp färgat</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17572,7 +16817,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
         <is>
           <t>-</t>
@@ -17630,8 +16874,6 @@
           <t>Underjordsbehållare 1,5 m³, glas ofärgat</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17647,7 +16889,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr">
         <is>
           <t>-</t>
@@ -17705,8 +16946,6 @@
           <t>Tömning underjordsbehållare 1,5 m³, glasförp ofärgat</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17722,7 +16961,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
           <t>-</t>
@@ -17780,8 +17018,6 @@
           <t>Underjordsbehållare 1,5 m³, metallförpackningar</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17797,7 +17033,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
           <t>-</t>
@@ -17855,8 +17090,6 @@
           <t>Tömning underjordsbehållare 1,5 m³, metallförpackningar</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
-      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17872,7 +17105,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
           <t>-</t>
@@ -17930,8 +17162,6 @@
           <t>Underjordsbehållare 1,5 m³, tidningar</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -17947,7 +17177,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
           <t>-</t>
@@ -18005,8 +17234,6 @@
           <t>Tömning underjordsbehållare 1,5 m³, tidningar</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18022,7 +17249,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr">
         <is>
           <t>-</t>
@@ -18080,8 +17306,6 @@
           <t>Underjordsbehållare 3,2 m³, plastförpackningar</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
-      <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18097,7 +17321,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr">
         <is>
           <t>-</t>
@@ -18155,8 +17378,6 @@
           <t>Tömning underjordsbehållare 3,2 m³, plastförpackningar</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18172,7 +17393,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr">
         <is>
           <t>-</t>
@@ -18230,8 +17450,6 @@
           <t>Underjordsbehållare 3,2 m³, restavfall</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
-      <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18247,7 +17465,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr">
         <is>
           <t>-</t>
@@ -18305,8 +17522,6 @@
           <t>Tömning underjordsbehållare 3,2 m³, restavfall</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
-      <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18322,7 +17537,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr">
         <is>
           <t>-</t>
@@ -18380,8 +17594,6 @@
           <t>Underjordsbehållare 5 m³, pappersförpackningar</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
-      <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18397,7 +17609,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr">
         <is>
           <t>-</t>
@@ -18455,8 +17666,6 @@
           <t>Tömning underjordsbehållare 5 m³, pappersförpackningar</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18472,7 +17681,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr">
         <is>
           <t>-</t>
@@ -18530,8 +17738,6 @@
           <t>Underjordsbehållare 5 m³, plastförpackningar</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18547,7 +17753,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr"/>
       <c r="O239" t="inlineStr">
         <is>
           <t>-</t>
@@ -18605,8 +17810,6 @@
           <t>Tömning underjordsbehållare 5 m³, plastförpackningar</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18622,7 +17825,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr">
         <is>
           <t>-</t>
@@ -18680,8 +17882,6 @@
           <t>Underjordsbehållare 0,8 m³, matavfall</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
-      <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18697,7 +17897,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr">
         <is>
           <t>-</t>
@@ -18755,8 +17954,6 @@
           <t>Tömning underjordsbehållare 0,8 m³, matavfall</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18772,7 +17969,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr"/>
       <c r="O242" t="inlineStr">
         <is>
           <t>-</t>
@@ -18830,8 +18026,6 @@
           <t>Utedass</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
-      <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -18847,7 +18041,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr"/>
       <c r="O243" t="inlineStr">
         <is>
           <t>-</t>
@@ -18905,8 +18098,6 @@
           <t>Vatten bostadshus</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
-      <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
           <t>3969.0</t>
@@ -18922,7 +18113,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr">
         <is>
           <t>-</t>
@@ -18933,7 +18123,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -18976,8 +18165,6 @@
           <t>Förbrukning</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
-      <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
           <t>24.5</t>
@@ -18993,7 +18180,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr">
         <is>
           <t>-</t>
@@ -19004,7 +18190,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -19047,8 +18232,6 @@
           <t>Grund och mätaravgift</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
-      <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
           <t>2999.5</t>
@@ -19064,7 +18247,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr">
         <is>
           <t>-</t>
@@ -19075,7 +18257,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -19118,8 +18299,6 @@
           <t>Förbrukning</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
           <t>24.5</t>
@@ -19135,7 +18314,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr">
         <is>
           <t>-</t>
@@ -19146,7 +18324,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -19189,8 +18366,6 @@
           <t>Vatten och avlopp</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
-      <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
           <t>6032.0</t>
@@ -19206,7 +18381,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr">
         <is>
           <t>-</t>
@@ -19217,7 +18391,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -19260,8 +18433,6 @@
           <t>Vatten och avlopp</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
-      <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
           <t>7746.0</t>
@@ -19277,7 +18448,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr">
         <is>
           <t>-</t>
@@ -19288,7 +18458,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -19331,8 +18500,6 @@
           <t>Vatten och avlopp</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
           <t>7746.0</t>
@@ -19348,7 +18515,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr">
         <is>
           <t>-</t>
@@ -19359,7 +18525,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -19402,8 +18567,6 @@
           <t>Extra avgift per 100kvm över 200kvm</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
-      <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
           <t>1639.0</t>
@@ -19419,7 +18582,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr">
         <is>
           <t>-</t>
@@ -19477,8 +18639,6 @@
           <t>Vatten och avlopp</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
-      <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
           <t>9609.0</t>
@@ -19494,7 +18654,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr">
         <is>
           <t>-</t>
@@ -19505,7 +18664,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -19548,8 +18706,6 @@
           <t>Vatten och avlopp mer än 2 lgh</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
           <t>2791.0</t>
@@ -19565,7 +18721,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr">
         <is>
           <t>-</t>
@@ -19623,8 +18778,6 @@
           <t>Vatten avlopp obebott</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
           <t>4293.0</t>
@@ -19640,7 +18793,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr">
         <is>
           <t>-</t>
@@ -19651,7 +18803,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -19694,8 +18845,6 @@
           <t>VA inom detaljplan obebyggd</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
-      <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
           <t>4128.0</t>
@@ -19711,7 +18860,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr">
         <is>
           <t>-</t>
@@ -19722,7 +18870,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -19745,7 +18892,6 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr">
         <is>
           <t>1</t>
@@ -19761,8 +18907,6 @@
           <t>VA, tillägg-avdrag</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
-      <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -19778,7 +18922,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr">
         <is>
           <t>-</t>
@@ -19789,7 +18932,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -19832,8 +18974,6 @@
           <t>VA Fast avgift - permanentbo.</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
           <t>6365.0</t>
@@ -19849,7 +18989,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr">
         <is>
           <t>-</t>
@@ -19860,7 +18999,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -19903,8 +19041,6 @@
           <t>Fast avgift camping</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
           <t>7746.0</t>
@@ -19920,7 +19056,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr">
         <is>
           <t>-</t>
@@ -19931,7 +19066,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -19974,8 +19108,6 @@
           <t>Extra för varje stuga</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
-      <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr">
         <is>
           <t>1231.0</t>
@@ -19991,7 +19123,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr">
         <is>
           <t>-</t>
@@ -20049,8 +19180,6 @@
           <t>Fast avgift va fritidshus</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
           <t>4410.0</t>
@@ -20066,7 +19195,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr">
         <is>
           <t>-</t>
@@ -20077,7 +19205,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -20120,8 +19247,6 @@
           <t>Vatten fritidshus</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
           <t>2716.0</t>
@@ -20137,7 +19262,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr">
         <is>
           <t>-</t>
@@ -20148,7 +19272,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -20191,8 +19314,6 @@
           <t>Vikt, glasförpackningar färgat</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
-      <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -20208,7 +19329,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr">
         <is>
           <t>-</t>
@@ -20266,8 +19386,6 @@
           <t>Vikt, glasförpackningar ofärgat</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -20283,7 +19401,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr">
         <is>
           <t>-</t>
@@ -20341,8 +19458,6 @@
           <t>Vikt, matavfall</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -20358,7 +19473,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr">
         <is>
           <t>-</t>
@@ -20416,8 +19530,6 @@
           <t>Viktavgift hushållsavfall</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
-      <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -20433,7 +19545,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr">
         <is>
           <t>-</t>
@@ -20491,8 +19602,6 @@
           <t>Viktavgift matavfall</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
           <t>2.24</t>
@@ -20508,7 +19617,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr">
         <is>
           <t>-</t>
@@ -20566,8 +19674,6 @@
           <t>Vikt över 60 kg, matavfall</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
           <t>4.0</t>
@@ -20583,7 +19689,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr">
         <is>
           <t>-</t>
@@ -20641,8 +19746,6 @@
           <t>Vikt, metallförpackningar</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
-      <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -20658,7 +19761,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr">
         <is>
           <t>-</t>
@@ -20716,8 +19818,6 @@
           <t>Vikt, pappersförpackningar</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
-      <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -20733,7 +19833,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr">
         <is>
           <t>-</t>
@@ -20791,8 +19890,6 @@
           <t>Vikt, plastförpackningar</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
       <c r="K270" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -20808,7 +19905,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr">
         <is>
           <t>-</t>
@@ -20866,8 +19962,6 @@
           <t>Vikt, restavfall</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -20883,7 +19977,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr">
         <is>
           <t>-</t>
@@ -20941,8 +20034,6 @@
           <t>Viktavgift restavfall</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
-      <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
           <t>4.4</t>
@@ -20958,7 +20049,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr">
         <is>
           <t>-</t>
@@ -21016,8 +20106,6 @@
           <t>Vikt över 60 kg, restavfall</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
-      <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
           <t>8.0</t>
@@ -21033,7 +20121,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr">
         <is>
           <t>-</t>
@@ -21091,8 +20178,6 @@
           <t>Vikt, tidningar</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
-      <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -21108,7 +20193,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr">
         <is>
           <t>-</t>
@@ -21166,8 +20250,6 @@
           <t>Vatten obebygg. inom detaljp.</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
-      <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
           <t>2200.0</t>
@@ -21183,7 +20265,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr">
         <is>
           <t>-</t>
@@ -21194,7 +20275,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Q275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -21237,8 +20317,6 @@
           <t>Volvo L60G</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
-      <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
           <t>162.4</t>
@@ -21254,7 +20332,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr">
         <is>
           <t>-</t>
@@ -21312,16 +20389,11 @@
           <t>Ändring på kund</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
-      <c r="J277" t="inlineStr"/>
-      <c r="K277" t="inlineStr"/>
-      <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr">
         <is>
           <t>-</t>
@@ -21488,7 +20560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21601,35 +20673,6 @@
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Kommentar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>EDP Standardtaxor / regelverk / manuell granskning</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Ej granskad</t>
-        </is>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>EDP-data får aldrig blandas mellan projekt.</t>
         </is>
       </c>
     </row>
@@ -21809,7 +20852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -21916,46 +20959,6 @@
       <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Kommentar</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr"/>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Taxakod</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Ej satt</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Befintlig Taxa_från_edp är fast. Standardtaxor får endast ge förslag/avvikelse.</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>Regelverk</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Ej granskad</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Standardflik för framtida spårning.</t>
         </is>
       </c>
     </row>
@@ -28541,7 +27544,6 @@
         </is>
       </c>
     </row>
-    <row r="216"/>
     <row r="217">
       <c r="D217" s="18" t="inlineStr">
         <is>
@@ -28702,7 +27704,6 @@
         </is>
       </c>
     </row>
-    <row r="222"/>
     <row r="223">
       <c r="D223" s="18" t="inlineStr">
         <is>
@@ -28863,7 +27864,6 @@
         </is>
       </c>
     </row>
-    <row r="228"/>
     <row r="229">
       <c r="D229" s="18" t="inlineStr">
         <is>
@@ -29024,7 +28024,6 @@
         </is>
       </c>
     </row>
-    <row r="234"/>
     <row r="235">
       <c r="D235" s="18" t="inlineStr">
         <is>
@@ -29185,7 +28184,6 @@
         </is>
       </c>
     </row>
-    <row r="240"/>
     <row r="241">
       <c r="D241" s="18" t="inlineStr">
         <is>
@@ -29346,7 +28344,6 @@
         </is>
       </c>
     </row>
-    <row r="246"/>
     <row r="247">
       <c r="D247" s="18" t="inlineStr">
         <is>
@@ -29507,7 +28504,6 @@
         </is>
       </c>
     </row>
-    <row r="252"/>
     <row r="253">
       <c r="D253" s="18" t="inlineStr">
         <is>
@@ -29668,7 +28664,6 @@
         </is>
       </c>
     </row>
-    <row r="258"/>
     <row r="259">
       <c r="D259" s="18" t="inlineStr">
         <is>
@@ -29829,7 +28824,6 @@
         </is>
       </c>
     </row>
-    <row r="264"/>
     <row r="265">
       <c r="D265" s="18" t="inlineStr">
         <is>
@@ -29990,7 +28984,6 @@
         </is>
       </c>
     </row>
-    <row r="270"/>
     <row r="271">
       <c r="D271" s="18" t="inlineStr">
         <is>
@@ -38767,7 +37760,6 @@
         </is>
       </c>
     </row>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="44" t="inlineStr">
         <is>

--- a/output/projects/Sorsele/excel/ArbetsExcel_Sorsele_byggd.xlsx
+++ b/output/projects/Sorsele/excel/ArbetsExcel_Sorsele_byggd.xlsx
@@ -66429,7 +66429,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>tvåbostadshus</t>
+          <t>en-och, tvåbostadshus</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr">
@@ -66742,7 +66742,7 @@
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>campingstuga, lägenhet</t>
+          <t>-lägenhet, campingstuga, lägenhet</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
@@ -66805,7 +66805,7 @@
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr"/>
@@ -66835,7 +66835,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Träavfall</t>
+          <t>Restavfall</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -66919,7 +66919,7 @@
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr"/>
@@ -66949,7 +66949,7 @@
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Träavfall</t>
+          <t>Restavfall</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -67017,7 +67017,7 @@
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>gemensam, mat, restavfall, uppsamlingsplats</t>
+          <t>gemensam, mat-, restavfall, uppsamlingsplats</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -67049,17 +67049,13 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G19" s="6" t="inlineStr"/>
       <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" s="6" t="inlineStr"/>
       <c r="J19" s="6" t="inlineStr"/>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
@@ -67069,7 +67065,7 @@
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -67097,20 +67093,12 @@
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>Tillfälle</t>
-        </is>
-      </c>
+      <c r="H20" s="6" t="inlineStr"/>
       <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>TILLFÄLLE</t>
-        </is>
-      </c>
+      <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -67120,7 +67108,7 @@
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>Avfallstyp kunde inte härledas.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -67264,7 +67252,7 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M23" s="6" t="inlineStr"/>
@@ -67779,7 +67767,7 @@
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>förpackningar, mat, restavfall</t>
+          <t>förpackningar, mat-, restavfall</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr">
@@ -67842,7 +67830,7 @@
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M33" s="6" t="inlineStr"/>
@@ -68062,7 +68050,7 @@
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>behållare, bottentömmande, mat, restavfall</t>
+          <t>behållare, bottentömmande, mat-, restavfall</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -68172,7 +68160,7 @@
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>240, kärl, mat, restavfall</t>
+          <t>240, kärl, mat-, restavfall</t>
         </is>
       </c>
       <c r="M39" s="6" t="inlineStr"/>
@@ -68392,7 +68380,7 @@
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>behållare, bottentömmande, mat, restavfall</t>
+          <t>behållare, bottentömmande, mat-, restavfall</t>
         </is>
       </c>
       <c r="M43" s="6" t="inlineStr">
@@ -68498,7 +68486,7 @@
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>140, kontors, kärl, returpapper</t>
+          <t>140, kontors-, kärl, returpapper</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr">
@@ -68541,7 +68529,7 @@
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>anvisning, egen, enligt, förbrukat, kontors, returpapper, överlämning</t>
+          <t>anvisning, egen, enligt, förbrukat, kontors-, returpapper, överlämning</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr">
@@ -68924,7 +68912,7 @@
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Träavfall</t>
+          <t>Matavfall</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
@@ -68983,7 +68971,7 @@
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Träavfall</t>
+          <t>Restavfall</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -69008,7 +68996,7 @@
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>140, 190, extra, kilogram, kärl, restavfall</t>
+          <t>140-190, extra, kilogram, kärl, restavfall</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
@@ -69248,17 +69236,13 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G60" s="6" t="inlineStr"/>
       <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" s="6" t="inlineStr"/>
       <c r="J60" s="6" t="inlineStr"/>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
@@ -69268,7 +69252,7 @@
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -69322,7 +69306,7 @@
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>140, 240, byte, ggr, kärl, liter, återtag</t>
+          <t>140-240, byte, ggr, kärl, liter, återtag</t>
         </is>
       </c>
       <c r="M61" s="6" t="inlineStr">
@@ -69381,7 +69365,7 @@
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>370, 660, byte, ggr, kärl, liter, återtag</t>
+          <t>370-660, byte, ggr, kärl, liter, återtag</t>
         </is>
       </c>
       <c r="M62" s="6" t="inlineStr">
@@ -69577,7 +69561,7 @@
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>140, 660, kärl</t>
+          <t>140-660, 5-10, kärl</t>
         </is>
       </c>
       <c r="M66" s="6" t="inlineStr">
@@ -69636,7 +69620,7 @@
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>140, 660, kärl</t>
+          <t>10-20, 140-660, kärl</t>
         </is>
       </c>
       <c r="M67" s="6" t="inlineStr">
@@ -69695,7 +69679,7 @@
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>140, 660, kärl</t>
+          <t>140-660, 20-30, kärl</t>
         </is>
       </c>
       <c r="M68" s="6" t="inlineStr">
@@ -70307,11 +70291,7 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>Matavfall</t>
-        </is>
-      </c>
+      <c r="G81" s="6" t="inlineStr"/>
       <c r="H81" s="6" t="inlineStr">
         <is>
           <t>Behållarvolym</t>
@@ -70325,7 +70305,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -70333,7 +70313,11 @@
           <t>matavfallspåsar</t>
         </is>
       </c>
-      <c r="M81" s="6" t="inlineStr"/>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -70358,11 +70342,7 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>Matavfall</t>
-        </is>
-      </c>
+      <c r="G82" s="6" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr">
         <is>
           <t>Behållarvolym</t>
@@ -70380,7 +70360,7 @@
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
@@ -70388,7 +70368,11 @@
           <t>matavfallspåsar</t>
         </is>
       </c>
-      <c r="M82" s="6" t="inlineStr"/>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -70460,17 +70444,13 @@
           <t>Hushåll</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G84" s="6" t="inlineStr"/>
       <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" s="6" t="inlineStr"/>
       <c r="J84" s="6" t="inlineStr"/>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
@@ -70480,7 +70460,7 @@
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -70930,7 +70910,7 @@
       </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
-          <t>bad, disk, tvättbrunn, upp</t>
+          <t>bad-, disk-och, tvättbrunn, upp</t>
         </is>
       </c>
       <c r="M93" s="6" t="inlineStr">
@@ -71017,27 +70997,23 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G95" s="6" t="inlineStr"/>
       <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" s="6" t="inlineStr"/>
       <c r="J95" s="6" t="inlineStr"/>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>5-25, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -71064,27 +71040,23 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G96" s="6" t="inlineStr"/>
       <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" s="6" t="inlineStr"/>
       <c r="J96" s="6" t="inlineStr"/>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>25-35, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -71111,27 +71083,23 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G97" s="6" t="inlineStr"/>
       <c r="H97" s="6" t="inlineStr"/>
       <c r="I97" s="6" t="inlineStr"/>
       <c r="J97" s="6" t="inlineStr"/>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>36-45, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M97" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -71158,27 +71126,23 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G98" s="6" t="inlineStr"/>
       <c r="H98" s="6" t="inlineStr"/>
       <c r="I98" s="6" t="inlineStr"/>
       <c r="J98" s="6" t="inlineStr"/>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>46-55, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -71228,7 +71192,7 @@
       </c>
       <c r="L99" s="6" t="inlineStr">
         <is>
-          <t>brunnslock, hantering, kilogram, som, väger</t>
+          <t>15-25, brunnslock, hantering, kilogram, som, väger</t>
         </is>
       </c>
       <c r="M99" s="6" t="inlineStr">
@@ -71440,11 +71404,7 @@
           <t>Flerbostad/verksamhet</t>
         </is>
       </c>
-      <c r="G104" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G104" s="6" t="inlineStr"/>
       <c r="H104" s="6" t="inlineStr">
         <is>
           <t>Volym</t>
@@ -71458,7 +71418,7 @@
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr">
@@ -71466,7 +71426,11 @@
           <t>brunn, budad, extra, ordinarie, samband, tank, tömning, upp</t>
         </is>
       </c>
-      <c r="M104" s="6" t="inlineStr"/>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -71502,7 +71466,7 @@
       </c>
       <c r="L105" s="6" t="inlineStr">
         <is>
-          <t>budning, inom, maj, oktober, ordinarie, tömningsperiod</t>
+          <t>budning, inom, maj-31, oktober, ordinarie, tömningsperiod</t>
         </is>
       </c>
       <c r="M105" s="6" t="inlineStr">
@@ -71545,7 +71509,7 @@
       </c>
       <c r="L106" s="6" t="inlineStr">
         <is>
-          <t>april, budning, nov, ordinarie, tömningsperiod, utanför</t>
+          <t>april, budning, nov-30, ordinarie, tömningsperiod, utanför</t>
         </is>
       </c>
       <c r="M106" s="6" t="inlineStr">
@@ -71769,7 +71733,7 @@
       </c>
       <c r="L110" s="6" t="inlineStr">
         <is>
-          <t>1000, 500, filtermassor, kilogram</t>
+          <t>500-1000, filtermassor, kilogram</t>
         </is>
       </c>
       <c r="M110" s="6" t="inlineStr">
@@ -72095,27 +72059,23 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G117" s="6" t="inlineStr"/>
       <c r="H117" s="6" t="inlineStr"/>
       <c r="I117" s="6" t="inlineStr"/>
       <c r="J117" s="6" t="inlineStr"/>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>5-25, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M117" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -72142,27 +72102,23 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G118" s="6" t="inlineStr"/>
       <c r="H118" s="6" t="inlineStr"/>
       <c r="I118" s="6" t="inlineStr"/>
       <c r="J118" s="6" t="inlineStr"/>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>25-35, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M118" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -72189,27 +72145,23 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G119" s="6" t="inlineStr"/>
       <c r="H119" s="6" t="inlineStr"/>
       <c r="I119" s="6" t="inlineStr"/>
       <c r="J119" s="6" t="inlineStr"/>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>36-45, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M119" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -72236,27 +72188,23 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G120" s="6" t="inlineStr"/>
       <c r="H120" s="6" t="inlineStr"/>
       <c r="I120" s="6" t="inlineStr"/>
       <c r="J120" s="6" t="inlineStr"/>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr">
         <is>
-          <t>dragning, extra, slang, vid</t>
+          <t>46-55, dragning, extra, slang, vid</t>
         </is>
       </c>
       <c r="M120" s="6" t="inlineStr">
         <is>
-          <t>Faktor kunde inte härledas från enhet/text.</t>
+          <t>Faktor kunde inte härledas från enhet/text. | Avfallstyp kunde inte härledas.</t>
         </is>
       </c>
     </row>
@@ -72306,7 +72254,7 @@
       </c>
       <c r="L121" s="6" t="inlineStr">
         <is>
-          <t>brunnslock, hantering, kilogram, som, väger</t>
+          <t>15-25, brunnslock, hantering, kilogram, som, väger</t>
         </is>
       </c>
       <c r="M121" s="6" t="inlineStr">
@@ -72561,11 +72509,7 @@
           <t>Slam</t>
         </is>
       </c>
-      <c r="G127" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G127" s="6" t="inlineStr"/>
       <c r="H127" s="6" t="inlineStr">
         <is>
           <t>Volym</t>
@@ -72579,7 +72523,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr">
@@ -72587,7 +72531,11 @@
           <t>budad, extra, ordinarie, samband, tank, tömning, upp</t>
         </is>
       </c>
-      <c r="M127" s="6" t="inlineStr"/>
+      <c r="M127" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -72623,7 +72571,7 @@
       </c>
       <c r="L128" s="6" t="inlineStr">
         <is>
-          <t>budning, inom, maj, oktober, ordinarie, tömningsperiod</t>
+          <t>budning, inom, maj-31, oktober, ordinarie, tömningsperiod</t>
         </is>
       </c>
       <c r="M128" s="6" t="inlineStr">
@@ -73137,11 +73085,7 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G139" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G139" s="6" t="inlineStr"/>
       <c r="H139" s="6" t="inlineStr">
         <is>
           <t>Vikt</t>
@@ -73155,15 +73099,19 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr">
         <is>
-          <t>kilogram, obehandlat, plastmatta, tapet, tjärpapp, träavfall</t>
-        </is>
-      </c>
-      <c r="M139" s="6" t="inlineStr"/>
+          <t>kilogram, plastmatta, tapet, tjärpapp, träavfall-obehandlat</t>
+        </is>
+      </c>
+      <c r="M139" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -73192,11 +73140,7 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G140" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G140" s="6" t="inlineStr"/>
       <c r="H140" s="6" t="inlineStr">
         <is>
           <t>Vikt</t>
@@ -73210,15 +73154,19 @@
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr">
         <is>
-          <t>behandlat, kilogram, plastmatta, tapet, tjärpapp, träavfall</t>
-        </is>
-      </c>
-      <c r="M140" s="6" t="inlineStr"/>
+          <t>kilogram, plastmatta, tapet, tjärpapp, träavfall-behandlat</t>
+        </is>
+      </c>
+      <c r="M140" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -73486,7 +73434,7 @@
       </c>
       <c r="L145" s="6" t="inlineStr">
         <is>
-          <t>fönster, karm, kilogram, planglas</t>
+          <t>fönster-och, karm, kilogram, planglas</t>
         </is>
       </c>
       <c r="M145" s="6" t="inlineStr">
@@ -73804,7 +73752,7 @@
       </c>
       <c r="L151" s="6" t="inlineStr">
         <is>
-          <t>stol, styck</t>
+          <t>styck, wc-stol</t>
         </is>
       </c>
       <c r="M151" s="6" t="inlineStr">
@@ -74297,7 +74245,7 @@
       </c>
       <c r="G161" s="6" t="inlineStr">
         <is>
-          <t>Farligt avfall</t>
+          <t>Elavfall</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr"/>
@@ -74456,7 +74404,11 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G164" s="6" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>Oljeavfall</t>
+        </is>
+      </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
           <t>Vikt</t>
@@ -74470,7 +74422,7 @@
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr">
@@ -74478,11 +74430,7 @@
           <t>förorenad, innehållande, kilogram, olja, pcb</t>
         </is>
       </c>
-      <c r="M164" s="6" t="inlineStr">
-        <is>
-          <t>Avfallstyp kunde inte härledas.</t>
-        </is>
-      </c>
+      <c r="M164" s="6" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
@@ -75006,11 +74954,7 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G174" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G174" s="6" t="inlineStr"/>
       <c r="H174" s="6" t="inlineStr">
         <is>
           <t>Vikt</t>
@@ -75024,7 +74968,7 @@
       </c>
       <c r="K174" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L174" s="6" t="inlineStr">
@@ -75032,7 +74976,11 @@
           <t>kilogram, kondensator, pcb, transformator</t>
         </is>
       </c>
-      <c r="M174" s="6" t="inlineStr"/>
+      <c r="M174" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -75795,7 +75743,7 @@
       </c>
       <c r="L188" s="6" t="inlineStr">
         <is>
-          <t>haltiga, kilogram, småkemikalier</t>
+          <t>hg-haltiga, kilogram, småkemikalier</t>
         </is>
       </c>
       <c r="M188" s="6" t="inlineStr">
@@ -77096,7 +77044,11 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G212" s="6" t="inlineStr"/>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>Oljeavfall</t>
+        </is>
+      </c>
       <c r="H212" s="6" t="inlineStr">
         <is>
           <t>Behållarvolym</t>
@@ -77110,7 +77062,7 @@
       </c>
       <c r="K212" s="6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="L212" s="6" t="inlineStr">
@@ -77118,11 +77070,7 @@
           <t>förorenad, liter, olja, pcb</t>
         </is>
       </c>
-      <c r="M212" s="6" t="inlineStr">
-        <is>
-          <t>Avfallstyp kunde inte härledas.</t>
-        </is>
-      </c>
+      <c r="M212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
@@ -77170,7 +77118,7 @@
       </c>
       <c r="L213" s="6" t="inlineStr">
         <is>
-          <t>färg, kilogram, lack, limburkar, lösning</t>
+          <t>färg-, kilogram, lack-, limburkar, lösning</t>
         </is>
       </c>
       <c r="M213" s="6" t="inlineStr">
@@ -77225,7 +77173,7 @@
       </c>
       <c r="L214" s="6" t="inlineStr">
         <is>
-          <t>aerosoler, färg, kilogram, lack, limburkar, lösning</t>
+          <t>aerosoler, färg-, kilogram, lack-, limburkar, lösning</t>
         </is>
       </c>
       <c r="M214" s="6" t="inlineStr">
@@ -77335,7 +77283,7 @@
       </c>
       <c r="L216" s="6" t="inlineStr">
         <is>
-          <t>etylketonperoxid, härdare, kilogram, metyl</t>
+          <t>härdare, kilogram, metyl-etylketonperoxid</t>
         </is>
       </c>
       <c r="M216" s="6" t="inlineStr">
@@ -77445,7 +77393,7 @@
       </c>
       <c r="L218" s="6" t="inlineStr">
         <is>
-          <t>färg, kilogram, lack, limburkar, vattenbaserade</t>
+          <t>färg-, kilogram, lack-, limburkar, vattenbaserade</t>
         </is>
       </c>
       <c r="M218" s="6" t="inlineStr">
@@ -77921,11 +77869,7 @@
           <t>ÅVC/verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G227" s="6" t="inlineStr">
-        <is>
-          <t>Batterier</t>
-        </is>
-      </c>
+      <c r="G227" s="6" t="inlineStr"/>
       <c r="H227" s="6" t="inlineStr">
         <is>
           <t>Styck</t>
@@ -77939,15 +77883,19 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr">
         <is>
-          <t>bil, bly, mcbatteri, styck</t>
-        </is>
-      </c>
-      <c r="M227" s="6" t="inlineStr"/>
+          <t>bil-, bly, mcbatteri, styck</t>
+        </is>
+      </c>
+      <c r="M227" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
@@ -78164,7 +78112,7 @@
       </c>
       <c r="L231" s="6" t="inlineStr">
         <is>
-          <t>avfall, fast, installation, kilogram</t>
+          <t>el-avfall, fast, installation, kilogram</t>
         </is>
       </c>
       <c r="M231" s="6" t="inlineStr"/>
@@ -78219,7 +78167,7 @@
       </c>
       <c r="L232" s="6" t="inlineStr">
         <is>
-          <t>avfall, kabel, kilogram</t>
+          <t>el-avfall, kabel, kilogram</t>
         </is>
       </c>
       <c r="M232" s="6" t="inlineStr"/>
@@ -78384,7 +78332,7 @@
       </c>
       <c r="L235" s="6" t="inlineStr">
         <is>
-          <t>boxstyck, frysskåp, kyl</t>
+          <t>-boxstyck, frysskåp, kyl-</t>
         </is>
       </c>
       <c r="M235" s="6" t="inlineStr"/>
@@ -78439,7 +78387,7 @@
       </c>
       <c r="L236" s="6" t="inlineStr">
         <is>
-          <t>boxfrån, frysskåp, kilogram, kyl, verksamhet</t>
+          <t>-boxfrån, frysskåp, kilogram, kyl-, verksamhet</t>
         </is>
       </c>
       <c r="M236" s="6" t="inlineStr"/>
@@ -78490,7 +78438,7 @@
       </c>
       <c r="L237" s="6" t="inlineStr">
         <is>
-          <t>diskmaskin, spis, styck, tvätt</t>
+          <t>diskmaskin, spis, styck, tvätt-</t>
         </is>
       </c>
       <c r="M237" s="6" t="inlineStr">
@@ -78545,7 +78493,7 @@
       </c>
       <c r="L238" s="6" t="inlineStr">
         <is>
-          <t>diskmaskin, kilogram, spis, tvätt, verksamhet</t>
+          <t>diskmaskin, kilogram, spis, tvätt-, verksamhet</t>
         </is>
       </c>
       <c r="M238" s="6" t="inlineStr">
@@ -78899,11 +78847,7 @@
           <t>Verksamhetsavfall</t>
         </is>
       </c>
-      <c r="G245" s="6" t="inlineStr">
-        <is>
-          <t>Träavfall</t>
-        </is>
-      </c>
+      <c r="G245" s="6" t="inlineStr"/>
       <c r="H245" s="6" t="inlineStr">
         <is>
           <t>Tillfälle</t>
@@ -78917,7 +78861,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr">
@@ -78925,7 +78869,11 @@
           <t>administrativ, avfallsregistret, rapporteringsavgift, tillfälle</t>
         </is>
       </c>
-      <c r="M245" s="6" t="inlineStr"/>
+      <c r="M245" s="6" t="inlineStr">
+        <is>
+          <t>Avfallstyp kunde inte härledas.</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
@@ -78973,7 +78921,7 @@
       </c>
       <c r="L246" s="6" t="inlineStr">
         <is>
-          <t>avlämnarintyg, hämtplatsportalen, kretsen, ombud, registrering, tillfälle</t>
+          <t>avlämnarintyg, el-kretsen, hämtplatsportalen, ombud, registrering, tillfälle</t>
         </is>
       </c>
       <c r="M246" s="6" t="inlineStr">
